--- a/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.7/backtests/window_40/return_vol_r2/post_rank_positive_return/rebalance_1d/close/close_annual_metrics.xlsx
@@ -466,12 +466,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -524,25 +524,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.09942783466812921</v>
+        <v>0.08232460354545634</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.2878231147978498</v>
+        <v>0.1689474504178964</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.4642395346398823</v>
+        <v>0.5251850138807228</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.6563898587104124</v>
+        <v>0.7621802723081466</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2264014838866976</v>
+        <v>0.12742404350528</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4993972895164029</v>
+        <v>0.7339041113803901</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>38.48699590324166</v>
+        <v>38.44845771248836</v>
       </c>
     </row>
     <row r="3">
@@ -552,25 +552,25 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.3111780571375943</v>
+        <v>0.04214373659445037</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.2478850184479432</v>
+        <v>0.2803904587409838</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-1.500839850667469</v>
+        <v>0.239160613220189</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-1.935509772104391</v>
+        <v>0.3599873869610445</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.3777614302737496</v>
+        <v>0.1835298258981242</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8516148506923369</v>
+        <v>0.2393230711955213</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>53.24875580692361</v>
+        <v>23.88071383762577</v>
       </c>
     </row>
     <row r="4">
@@ -580,25 +580,25 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.1038971448156993</v>
+        <v>0.01950290607670979</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.22362614409413</v>
+        <v>0.232888362029084</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.5048272799817968</v>
+        <v>0.1383010620364247</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.7655982272549097</v>
+        <v>0.1983506306948086</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1634168878294199</v>
+        <v>0.2068580002945761</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.6634278802317158</v>
+        <v>0.0982168648312339</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>44.06935588349358</v>
+        <v>57.05573939254476</v>
       </c>
     </row>
     <row r="5">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.1166700575931614</v>
+        <v>0.03591629369508631</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.2227561880608683</v>
+        <v>0.267584709800415</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.5599110697273521</v>
+        <v>0.2153064801222539</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.8238659967373867</v>
+        <v>0.2993973828895153</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1377284887612046</v>
+        <v>0.1926811722724028</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.8841573708373004</v>
+        <v>0.194247722237827</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>41.6125291736308</v>
+        <v>41.68034145164308</v>
       </c>
     </row>
     <row r="6">
@@ -636,25 +636,25 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2147469630074317</v>
+        <v>0.2181800258190518</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2474676404215274</v>
+        <v>0.2609343353344251</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.8798605235049698</v>
+        <v>0.8588671975999402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.193951992088679</v>
+        <v>1.173341555477326</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.2291540755432088</v>
+        <v>0.2269037508120766</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.9754609695882794</v>
+        <v>1.000939829185769</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>56.62930836270844</v>
+        <v>49.50459257226871</v>
       </c>
     </row>
     <row r="7">
@@ -664,25 +664,25 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.01101812535318514</v>
+        <v>0.3198677356617181</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3388160647227817</v>
+        <v>0.389583647825909</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.06602596989920702</v>
+        <v>1.446611983478943</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0900336116669047</v>
+        <v>2.311795346498086</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.2190847240542417</v>
+        <v>0.153226202479075</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.09076754941970273</v>
+        <v>4.267703966046774</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>35.06383430724957</v>
+        <v>39.01432263232676</v>
       </c>
     </row>
   </sheetData>
